--- a/data/trans_dic/P34B02_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P34B02_R-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, 3 veces por semana o más</t>
+          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 10,43</t>
+          <t>5,3; 10,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 11,7</t>
+          <t>6,18; 12,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 25,59</t>
+          <t>17,83; 25,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,77</t>
+          <t>3,23; 9,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,34</t>
+          <t>5,57; 11,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,79; 26,01</t>
+          <t>18,8; 26,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,76</t>
+          <t>5,02; 8,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,66</t>
+          <t>6,65; 10,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,23; 24,69</t>
+          <t>19,13; 24,43</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,45</t>
+          <t>3,19; 7,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,35; 14,79</t>
+          <t>8,06; 14,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 25,81</t>
+          <t>17,5; 26,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,96</t>
+          <t>2,17; 7,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 9,85</t>
+          <t>4,15; 9,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,06; 21,95</t>
+          <t>15,14; 21,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,42</t>
+          <t>3,21; 6,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,32</t>
+          <t>6,98; 11,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 22,7</t>
+          <t>17,26; 22,64</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,38</t>
+          <t>3,46; 7,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,63</t>
+          <t>4,46; 8,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 17,3</t>
+          <t>4,07; 17,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,15</t>
+          <t>2,37; 8,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 12,61</t>
+          <t>4,15; 13,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 16,79</t>
+          <t>8,16; 16,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,73</t>
+          <t>3,61; 6,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,85</t>
+          <t>4,89; 8,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 15,75</t>
+          <t>4,92; 16,0</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,37</t>
+          <t>2,9; 5,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 7,47</t>
+          <t>4,74; 7,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 20,67</t>
+          <t>15,24; 21,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,51</t>
+          <t>2,51; 5,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,09</t>
+          <t>3,92; 6,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 15,49</t>
+          <t>5,5; 15,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 4,88</t>
+          <t>3,09; 4,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,01</t>
+          <t>4,79; 6,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 17,08</t>
+          <t>10,14; 17,39</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,53</t>
+          <t>4,0; 8,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,94</t>
+          <t>4,76; 8,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,1; 18,54</t>
+          <t>11,06; 18,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,42</t>
+          <t>1,24; 3,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,59</t>
+          <t>3,49; 6,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,74</t>
+          <t>6,31; 10,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,78</t>
+          <t>2,67; 4,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,05</t>
+          <t>4,56; 7,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 12,46</t>
+          <t>8,52; 12,69</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,49</t>
+          <t>5,01; 11,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,88; 15,32</t>
+          <t>7,79; 15,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,1; 45,02</t>
+          <t>23,08; 44,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,51</t>
+          <t>3,22; 5,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,94</t>
+          <t>2,54; 4,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,24</t>
+          <t>7,98; 12,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,23</t>
+          <t>3,85; 6,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,53</t>
+          <t>3,99; 6,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,88; 19,34</t>
+          <t>12,68; 18,92</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,25</t>
+          <t>4,6; 6,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,46</t>
+          <t>6,6; 8,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,66; 20,12</t>
+          <t>13,43; 19,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 4,52</t>
+          <t>3,19; 4,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,07</t>
+          <t>4,54; 6,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,32; 13,93</t>
+          <t>10,15; 13,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,15</t>
+          <t>4,09; 5,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 6,92</t>
+          <t>5,79; 7,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,17; 16,48</t>
+          <t>13,2; 16,71</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, 3 veces por semana o más</t>
+          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23910; 45613</t>
+          <t>23172; 45924</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25300; 50205</t>
+          <t>26524; 53568</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88628; 129259</t>
+          <t>90078; 131076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9533; 27566</t>
+          <t>10161; 29321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19867; 39341</t>
+          <t>19318; 39252</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84059; 116335</t>
+          <t>84106; 116548</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37438; 65842</t>
+          <t>37736; 67147</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50957; 82762</t>
+          <t>51580; 84752</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>183193; 235195</t>
+          <t>182197; 232659</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13576; 31204</t>
+          <t>13371; 31097</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31499; 55788</t>
+          <t>30392; 55580</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78980; 116726</t>
+          <t>79142; 117895</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8025; 23536</t>
+          <t>7338; 23817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16047; 36662</t>
+          <t>15450; 35779</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57514; 83834</t>
+          <t>57819; 83529</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25562; 48595</t>
+          <t>24268; 48777</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52035; 84818</t>
+          <t>52353; 84684</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>142311; 189377</t>
+          <t>143941; 188874</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21861; 46364</t>
+          <t>21752; 44914</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22594; 45051</t>
+          <t>23281; 46146</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20516; 115579</t>
+          <t>27200; 118050</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5970; 21205</t>
+          <t>6153; 20954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6405; 20948</t>
+          <t>6899; 21899</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13611; 28026</t>
+          <t>13612; 27374</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31390; 59833</t>
+          <t>32053; 60142</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33651; 60893</t>
+          <t>33651; 61754</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31001; 131581</t>
+          <t>41066; 133612</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34780; 62269</t>
+          <t>33635; 61346</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52558; 85833</t>
+          <t>54504; 87259</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>154400; 213130</t>
+          <t>157138; 219449</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19108; 42136</t>
+          <t>19213; 41312</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32628; 58547</t>
+          <t>32363; 57396</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57768; 151386</t>
+          <t>53808; 148577</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58858; 93840</t>
+          <t>59516; 95101</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94920; 138395</t>
+          <t>94607; 137626</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>201400; 342967</t>
+          <t>203573; 349240</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20823; 43552</t>
+          <t>20407; 42247</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29796; 55464</t>
+          <t>29533; 54349</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52624; 87895</t>
+          <t>52418; 87962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9756; 26047</t>
+          <t>9474; 26455</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25356; 48687</t>
+          <t>25779; 49860</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52864; 90122</t>
+          <t>52932; 88718</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33526; 60818</t>
+          <t>33945; 61851</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61617; 95848</t>
+          <t>61942; 96507</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>110820; 163619</t>
+          <t>111858; 166592</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12763; 30534</t>
+          <t>13310; 29840</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22631; 44005</t>
+          <t>22383; 44377</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60369; 108271</t>
+          <t>55515; 107338</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34788; 61172</t>
+          <t>35752; 62892</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28365; 53424</t>
+          <t>27536; 52148</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>61159; 93130</t>
+          <t>60693; 92989</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52034; 85656</t>
+          <t>52974; 85407</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55740; 89442</t>
+          <t>54643; 89688</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>129005; 193648</t>
+          <t>126946; 189480</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>159452; 213906</t>
+          <t>157320; 212745</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>226839; 286386</t>
+          <t>223497; 289099</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>460661; 678178</t>
+          <t>452856; 673542</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112599; 160374</t>
+          <t>113339; 159997</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>158233; 214319</t>
+          <t>160445; 212359</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>368818; 497810</t>
+          <t>362515; 497815</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>286194; 358603</t>
+          <t>284783; 358023</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>399903; 478913</t>
+          <t>400384; 487045</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>914420; 1144770</t>
+          <t>916420; 1160481</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B02_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P34B02_R-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 10,5</t>
+          <t>5,34; 10,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 12,48</t>
+          <t>6,13; 12,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,83; 25,94</t>
+          <t>16,93; 24,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,32</t>
+          <t>3,3; 8,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 11,31</t>
+          <t>5,49; 11,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,8; 26,06</t>
+          <t>18,3; 25,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,93</t>
+          <t>5,08; 8,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,92</t>
+          <t>6,48; 10,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,13; 24,43</t>
+          <t>18,57; 23,56</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,43</t>
+          <t>3,26; 7,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 14,73</t>
+          <t>8,32; 14,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,5; 26,07</t>
+          <t>17,03; 24,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,05</t>
+          <t>2,4; 7,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,61</t>
+          <t>4,49; 10,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 21,87</t>
+          <t>14,35; 20,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,45</t>
+          <t>3,28; 6,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 11,3</t>
+          <t>7,14; 11,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,26; 22,64</t>
+          <t>16,94; 22,05</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,15</t>
+          <t>3,53; 7,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,84</t>
+          <t>4,68; 9,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 17,67</t>
+          <t>13,04; 20,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,06</t>
+          <t>2,32; 8,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 13,18</t>
+          <t>4,26; 12,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,16; 16,4</t>
+          <t>8,11; 15,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,77</t>
+          <t>3,72; 6,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,98</t>
+          <t>4,99; 9,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 16,0</t>
+          <t>12,67; 18,65</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,29</t>
+          <t>2,92; 5,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,59</t>
+          <t>4,82; 7,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,24; 21,29</t>
+          <t>15,28; 20,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,4</t>
+          <t>2,4; 5,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,95</t>
+          <t>4,04; 7,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 15,2</t>
+          <t>12,42; 16,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,94</t>
+          <t>3,08; 4,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 6,97</t>
+          <t>4,81; 6,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 17,39</t>
+          <t>14,5; 18,11</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,27</t>
+          <t>3,98; 8,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,76</t>
+          <t>4,68; 8,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,06; 18,56</t>
+          <t>12,23; 18,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,47</t>
+          <t>1,32; 3,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,75</t>
+          <t>3,33; 6,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,58</t>
+          <t>8,83; 12,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,86</t>
+          <t>2,62; 4,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,1</t>
+          <t>4,54; 7,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,52; 12,69</t>
+          <t>10,64; 14,25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 11,23</t>
+          <t>4,64; 11,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 15,45</t>
+          <t>7,53; 15,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,08; 44,63</t>
+          <t>26,52; 46,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,67</t>
+          <t>3,16; 5,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,82</t>
+          <t>2,51; 4,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,98; 12,22</t>
+          <t>7,81; 12,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,21</t>
+          <t>3,84; 6,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,55</t>
+          <t>4,07; 6,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,68; 18,92</t>
+          <t>12,93; 18,59</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,22</t>
+          <t>4,65; 6,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 8,54</t>
+          <t>6,75; 8,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,43; 19,98</t>
+          <t>17,68; 20,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,51</t>
+          <t>3,15; 4,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,01</t>
+          <t>4,51; 6,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,93</t>
+          <t>12,54; 14,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,14</t>
+          <t>4,09; 5,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,04</t>
+          <t>5,78; 7,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,2; 16,71</t>
+          <t>15,44; 17,27</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107684</t>
+          <t>112211</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99089</t>
+          <t>104494</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>206773</t>
+          <t>216705</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23172; 45924</t>
+          <t>23361; 45700</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26524; 53568</t>
+          <t>26312; 51574</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90078; 131076</t>
+          <t>93218; 132814</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10161; 29321</t>
+          <t>10372; 28048</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19318; 39252</t>
+          <t>19050; 39882</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84106; 116548</t>
+          <t>88920; 122671</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37736; 67147</t>
+          <t>38207; 65725</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51580; 84752</t>
+          <t>50279; 82025</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>182197; 232659</t>
+          <t>192527; 244276</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95668</t>
+          <t>99938</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69318</t>
+          <t>73823</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>164986</t>
+          <t>173760</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13371; 31097</t>
+          <t>13654; 31103</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30392; 55580</t>
+          <t>31385; 56267</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79142; 117895</t>
+          <t>82306; 120665</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7338; 23817</t>
+          <t>8111; 24856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15450; 35779</t>
+          <t>16722; 38579</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57819; 83529</t>
+          <t>60621; 87263</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24268; 48777</t>
+          <t>24842; 47911</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52353; 84684</t>
+          <t>53507; 87198</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>143941; 188874</t>
+          <t>153394; 199686</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69123</t>
+          <t>78160</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88708</t>
+          <t>99482</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21752; 44914</t>
+          <t>22211; 44511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23281; 46146</t>
+          <t>24451; 48231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27200; 118050</t>
+          <t>61485; 97124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6153; 20954</t>
+          <t>6025; 21793</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6899; 21899</t>
+          <t>7079; 21449</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13612; 27374</t>
+          <t>15202; 29291</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32053; 60142</t>
+          <t>33102; 60384</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33651; 61754</t>
+          <t>34353; 62804</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41066; 133612</t>
+          <t>83538; 122932</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183127</t>
+          <t>200751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>122263</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>295169</t>
+          <t>323014</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33635; 61346</t>
+          <t>33870; 62205</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54504; 87259</t>
+          <t>55388; 88909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>157138; 219449</t>
+          <t>172108; 232152</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19213; 41312</t>
+          <t>18351; 41335</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32363; 57396</t>
+          <t>33378; 60481</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53808; 148577</t>
+          <t>106882; 142371</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59516; 95101</t>
+          <t>59332; 95881</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94607; 137626</t>
+          <t>94954; 137723</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>203573; 349240</t>
+          <t>288133; 359977</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68617</t>
+          <t>85529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72095</t>
+          <t>86402</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>171930</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20407; 42247</t>
+          <t>20303; 42281</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29533; 54349</t>
+          <t>29031; 53774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52418; 87962</t>
+          <t>69317; 106783</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9474; 26455</t>
+          <t>10030; 25887</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25779; 49860</t>
+          <t>24554; 49116</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52932; 88718</t>
+          <t>73261; 103053</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33945; 61851</t>
+          <t>33282; 62188</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61942; 96507</t>
+          <t>61645; 96675</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>111858; 166592</t>
+          <t>148577; 199019</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82023</t>
+          <t>86433</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75507</t>
+          <t>82835</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>157530</t>
+          <t>169269</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13310; 29840</t>
+          <t>12317; 29997</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22383; 44377</t>
+          <t>21618; 43353</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55515; 107338</t>
+          <t>62904; 110785</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35752; 62892</t>
+          <t>35098; 62720</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27536; 52148</t>
+          <t>27131; 52439</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60693; 92989</t>
+          <t>65906; 101847</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52974; 85407</t>
+          <t>52761; 83347</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54643; 89688</t>
+          <t>55774; 90279</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>126946; 189480</t>
+          <t>139765; 200995</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>606242</t>
+          <t>663022</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>447636</t>
+          <t>491138</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1053878</t>
+          <t>1154159</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>157320; 212745</t>
+          <t>158886; 213877</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>223497; 289099</t>
+          <t>228400; 288949</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>452856; 673542</t>
+          <t>607544; 712536</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113339; 159997</t>
+          <t>111729; 159391</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>160445; 212359</t>
+          <t>159397; 213263</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>362515; 497815</t>
+          <t>455100; 528622</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>284783; 358023</t>
+          <t>284788; 359118</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>400384; 487045</t>
+          <t>399562; 485807</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>916420; 1160481</t>
+          <t>1090906; 1220193</t>
         </is>
       </c>
     </row>
